--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-22).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-22).xlsx
@@ -935,31 +935,31 @@
     <t>214</t>
   </si>
   <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>R$ 4.962,64</t>
-  </si>
-  <si>
-    <t>52.4</t>
-  </si>
-  <si>
-    <t>31.0</t>
-  </si>
-  <si>
-    <t>5.37</t>
-  </si>
-  <si>
-    <t>18.0</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>4.9</t>
-  </si>
-  <si>
-    <t>43.7%</t>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 4.988,97</t>
+  </si>
+  <si>
+    <t>52.6</t>
+  </si>
+  <si>
+    <t>30.9</t>
+  </si>
+  <si>
+    <t>5.35</t>
+  </si>
+  <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>6.0</t>
+  </si>
+  <si>
+    <t>42.4%</t>
   </si>
   <si>
     <t>16.0%</t>
@@ -971,58 +971,58 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>3.8%</t>
+    <t>3.6%</t>
   </si>
   <si>
     <t>1.3%</t>
   </si>
   <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>6.7%</t>
-  </si>
-  <si>
-    <t>2.5%</t>
-  </si>
-  <si>
-    <t>2.8%</t>
-  </si>
-  <si>
-    <t>895.0</t>
-  </si>
-  <si>
-    <t>726.0</t>
-  </si>
-  <si>
-    <t>72.0</t>
-  </si>
-  <si>
-    <t>24.0</t>
-  </si>
-  <si>
-    <t>171.0</t>
-  </si>
-  <si>
-    <t>59.0</t>
-  </si>
-  <si>
-    <t>12.0</t>
-  </si>
-  <si>
-    <t>302.0</t>
-  </si>
-  <si>
-    <t>114.0</t>
-  </si>
-  <si>
-    <t>129.0</t>
-  </si>
-  <si>
-    <t>0.8%</t>
-  </si>
-  <si>
-    <t>36.0</t>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>6.4%</t>
+  </si>
+  <si>
+    <t>2.9%</t>
+  </si>
+  <si>
+    <t>3.0%</t>
+  </si>
+  <si>
+    <t>1083.0</t>
+  </si>
+  <si>
+    <t>875.0</t>
+  </si>
+  <si>
+    <t>89.0</t>
+  </si>
+  <si>
+    <t>26.0</t>
+  </si>
+  <si>
+    <t>199.0</t>
+  </si>
+  <si>
+    <t>73.0</t>
+  </si>
+  <si>
+    <t>13.0</t>
+  </si>
+  <si>
+    <t>351.0</t>
+  </si>
+  <si>
+    <t>157.0</t>
+  </si>
+  <si>
+    <t>163.0</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>38.0</t>
   </si>
   <si>
     <t>1</t>
@@ -2054,7 +2054,7 @@
         <v>19506</v>
       </c>
       <c r="B5" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C5" s="4">
         <v>51</v>
@@ -2084,35 +2084,93 @@
         <v>58</v>
       </c>
       <c r="L5" s="4"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="6"/>
-      <c r="O5" s="6"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="8"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
-      <c r="X5" s="9"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="9"/>
-      <c r="AA5" s="9"/>
-      <c r="AB5" s="9"/>
-      <c r="AC5" s="9"/>
-      <c r="AD5" s="6"/>
-      <c r="AE5" s="6"/>
-      <c r="AF5" s="6"/>
-      <c r="AG5" s="6"/>
-      <c r="AH5" s="6"/>
-      <c r="AI5" s="6"/>
-      <c r="AJ5" s="6"/>
-      <c r="AK5" s="6"/>
-      <c r="AL5" s="6"/>
-      <c r="AM5" s="6"/>
-      <c r="AN5" s="9"/>
-      <c r="AO5" s="6"/>
+      <c r="M5" s="5">
+        <v>7831.6999999999998</v>
+      </c>
+      <c r="N5" s="6">
+        <v>80</v>
+      </c>
+      <c r="O5" s="6">
+        <v>51</v>
+      </c>
+      <c r="P5" s="7">
+        <v>5.1870129870129871</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>19.188562745098039</v>
+      </c>
+      <c r="R5" s="8">
+        <v>7.965358823529411</v>
+      </c>
+      <c r="S5" s="8">
+        <v>6</v>
+      </c>
+      <c r="T5" s="9">
+        <v>0.13725490196078433</v>
+      </c>
+      <c r="U5" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="V5" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="W5" s="9">
+        <v>0</v>
+      </c>
+      <c r="X5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="9">
+        <v>0.019607843137254902</v>
+      </c>
+      <c r="AB5" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AC5" s="9">
+        <v>0.039215686274509803</v>
+      </c>
+      <c r="AD5" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE5" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM5" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP5" s="4">
         <v>58</v>
       </c>
@@ -2248,7 +2306,7 @@
         <v>19508</v>
       </c>
       <c r="B7" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C7" s="4">
         <v>51</v>
@@ -2278,35 +2336,93 @@
         <v>58</v>
       </c>
       <c r="L7" s="4"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="6"/>
-      <c r="O7" s="6"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="8"/>
-      <c r="T7" s="9"/>
-      <c r="U7" s="9"/>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="9"/>
-      <c r="AA7" s="9"/>
-      <c r="AB7" s="9"/>
-      <c r="AC7" s="9"/>
-      <c r="AD7" s="6"/>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
-      <c r="AI7" s="6"/>
-      <c r="AJ7" s="6"/>
-      <c r="AK7" s="6"/>
-      <c r="AL7" s="6"/>
-      <c r="AM7" s="6"/>
-      <c r="AN7" s="9"/>
-      <c r="AO7" s="6"/>
+      <c r="M7" s="5">
+        <v>8005.8900000000003</v>
+      </c>
+      <c r="N7" s="6">
+        <v>75</v>
+      </c>
+      <c r="O7" s="6">
+        <v>32</v>
+      </c>
+      <c r="P7" s="7">
+        <v>10.6356765625</v>
+      </c>
+      <c r="Q7" s="8">
+        <v>18.666146874999999</v>
+      </c>
+      <c r="R7" s="8">
+        <v>2.7781250000000002</v>
+      </c>
+      <c r="S7" s="8">
+        <v>7</v>
+      </c>
+      <c r="T7" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U7" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="V7" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="W7" s="9">
+        <v>0</v>
+      </c>
+      <c r="X7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="9">
+        <v>0.03125</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP7" s="4">
         <v>58</v>
       </c>
@@ -2502,7 +2618,7 @@
         <v>19511</v>
       </c>
       <c r="B9" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C9" s="4">
         <v>51</v>
@@ -2532,35 +2648,93 @@
         <v>58</v>
       </c>
       <c r="L9" s="4"/>
-      <c r="M9" s="5"/>
-      <c r="N9" s="6"/>
-      <c r="O9" s="6"/>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="8"/>
-      <c r="T9" s="9"/>
-      <c r="U9" s="9"/>
-      <c r="V9" s="9"/>
-      <c r="W9" s="9"/>
-      <c r="X9" s="9"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="9"/>
-      <c r="AA9" s="9"/>
-      <c r="AB9" s="9"/>
-      <c r="AC9" s="9"/>
-      <c r="AD9" s="6"/>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="6"/>
-      <c r="AI9" s="6"/>
-      <c r="AJ9" s="6"/>
-      <c r="AK9" s="6"/>
-      <c r="AL9" s="6"/>
-      <c r="AM9" s="6"/>
-      <c r="AN9" s="9"/>
-      <c r="AO9" s="6"/>
+      <c r="M9" s="5">
+        <v>6809.8100000000004</v>
+      </c>
+      <c r="N9" s="6">
+        <v>63</v>
+      </c>
+      <c r="O9" s="6">
+        <v>42</v>
+      </c>
+      <c r="P9" s="7">
+        <v>4.0827951612903224</v>
+      </c>
+      <c r="Q9" s="8">
+        <v>14.398809523809524</v>
+      </c>
+      <c r="R9" s="8">
+        <v>4.1743902439024394</v>
+      </c>
+      <c r="S9" s="8">
+        <v>6.1500000000000004</v>
+      </c>
+      <c r="T9" s="9">
+        <v>0.54761904761904767</v>
+      </c>
+      <c r="U9" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0</v>
+      </c>
+      <c r="W9" s="9">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="9">
+        <v>0.023809523809523808</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0.071428571428571425</v>
+      </c>
+      <c r="AC9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE9" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP9" s="4">
         <v>58</v>
       </c>
@@ -2754,7 +2928,7 @@
         <v>19513</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>51</v>
@@ -2784,35 +2958,93 @@
         <v>58</v>
       </c>
       <c r="L11" s="4"/>
-      <c r="M11" s="5"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="8"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="6"/>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
-      <c r="AI11" s="6"/>
-      <c r="AJ11" s="6"/>
-      <c r="AK11" s="6"/>
-      <c r="AL11" s="6"/>
-      <c r="AM11" s="6"/>
-      <c r="AN11" s="9"/>
-      <c r="AO11" s="6"/>
+      <c r="M11" s="5">
+        <v>10858.040000000001</v>
+      </c>
+      <c r="N11" s="6">
+        <v>84</v>
+      </c>
+      <c r="O11" s="6">
+        <v>65</v>
+      </c>
+      <c r="P11" s="7">
+        <v>6.0252941176470589</v>
+      </c>
+      <c r="Q11" s="8">
+        <v>15.731026153846154</v>
+      </c>
+      <c r="R11" s="8">
+        <v>3.8396825396825398</v>
+      </c>
+      <c r="S11" s="8">
+        <v>6</v>
+      </c>
+      <c r="T11" s="9">
+        <v>0.49230769230769234</v>
+      </c>
+      <c r="U11" s="9">
+        <v>0.12307692307692308</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="W11" s="9">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="Y11" s="9">
+        <v>0.030769230769230771</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="9">
+        <v>0.046153846153846156</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="AC11" s="9">
+        <v>0.061538461538461542</v>
+      </c>
+      <c r="AD11" s="6">
+        <v>13</v>
+      </c>
+      <c r="AE11" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>2</v>
+      </c>
+      <c r="AJ11" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL11" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM11" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN11" s="9">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="AO11" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP11" s="4">
         <v>58</v>
       </c>
@@ -3924,7 +4156,9 @@
       <c r="N19" s="6">
         <v>56</v>
       </c>
-      <c r="O19" s="6"/>
+      <c r="O19" s="6">
+        <v>31</v>
+      </c>
       <c r="P19" s="7">
         <v>8.1009090909090915</v>
       </c>
@@ -3934,31 +4168,75 @@
       <c r="R19" s="8">
         <v>10.443333333333333</v>
       </c>
-      <c r="S19" s="8"/>
+      <c r="S19" s="8">
+        <v>7</v>
+      </c>
       <c r="T19" s="9">
         <v>0.096774193548387094</v>
       </c>
-      <c r="U19" s="9"/>
-      <c r="V19" s="9"/>
-      <c r="W19" s="9"/>
-      <c r="X19" s="9"/>
-      <c r="Y19" s="9"/>
-      <c r="Z19" s="9"/>
-      <c r="AA19" s="9"/>
-      <c r="AB19" s="9"/>
-      <c r="AC19" s="9"/>
-      <c r="AD19" s="6"/>
-      <c r="AE19" s="6"/>
-      <c r="AF19" s="6"/>
-      <c r="AG19" s="6"/>
-      <c r="AH19" s="6"/>
-      <c r="AI19" s="6"/>
-      <c r="AJ19" s="6"/>
-      <c r="AK19" s="6"/>
-      <c r="AL19" s="6"/>
-      <c r="AM19" s="6"/>
-      <c r="AN19" s="9"/>
-      <c r="AO19" s="6"/>
+      <c r="U19" s="9">
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="V19" s="9">
+        <v>0.16129032258064516</v>
+      </c>
+      <c r="W19" s="9">
+        <v>0</v>
+      </c>
+      <c r="X19" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="Y19" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="Z19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AB19" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="AC19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="6">
+        <v>9</v>
+      </c>
+      <c r="AE19" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF19" s="6">
+        <v>5</v>
+      </c>
+      <c r="AG19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AJ19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL19" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM19" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP19" s="4">
         <v>58</v>
       </c>
@@ -4468,7 +4746,7 @@
         <v>19529</v>
       </c>
       <c r="B23" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C23" s="4">
         <v>51</v>
@@ -4498,35 +4776,93 @@
         <v>58</v>
       </c>
       <c r="L23" s="4"/>
-      <c r="M23" s="5"/>
-      <c r="N23" s="6"/>
-      <c r="O23" s="6"/>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="8"/>
-      <c r="T23" s="9"/>
-      <c r="U23" s="9"/>
-      <c r="V23" s="9"/>
-      <c r="W23" s="9"/>
-      <c r="X23" s="9"/>
-      <c r="Y23" s="9"/>
-      <c r="Z23" s="9"/>
-      <c r="AA23" s="9"/>
-      <c r="AB23" s="9"/>
-      <c r="AC23" s="9"/>
-      <c r="AD23" s="6"/>
-      <c r="AE23" s="6"/>
-      <c r="AF23" s="6"/>
-      <c r="AG23" s="6"/>
-      <c r="AH23" s="6"/>
-      <c r="AI23" s="6"/>
-      <c r="AJ23" s="6"/>
-      <c r="AK23" s="6"/>
-      <c r="AL23" s="6"/>
-      <c r="AM23" s="6"/>
-      <c r="AN23" s="9"/>
-      <c r="AO23" s="6"/>
+      <c r="M23" s="5">
+        <v>10102.25</v>
+      </c>
+      <c r="N23" s="6">
+        <v>107</v>
+      </c>
+      <c r="O23" s="6">
+        <v>73</v>
+      </c>
+      <c r="P23" s="7">
+        <v>7.2909523809523806</v>
+      </c>
+      <c r="Q23" s="8">
+        <v>19.160273972602742</v>
+      </c>
+      <c r="R23" s="8">
+        <v>4.4726847222222226</v>
+      </c>
+      <c r="S23" s="8">
+        <v>7</v>
+      </c>
+      <c r="T23" s="9">
+        <v>0.17808219178082191</v>
+      </c>
+      <c r="U23" s="9">
+        <v>0.12328767123287671</v>
+      </c>
+      <c r="V23" s="9">
+        <v>0</v>
+      </c>
+      <c r="W23" s="9">
+        <v>0</v>
+      </c>
+      <c r="X23" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="9">
+        <v>0.082191780821917804</v>
+      </c>
+      <c r="AB23" s="9">
+        <v>0.054794520547945202</v>
+      </c>
+      <c r="AC23" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD23" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE23" s="6">
+        <v>9</v>
+      </c>
+      <c r="AF23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="6">
+        <v>6</v>
+      </c>
+      <c r="AL23" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM23" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP23" s="4">
         <v>58</v>
       </c>
@@ -4980,7 +5316,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>51</v>
@@ -5010,35 +5346,93 @@
         <v>58</v>
       </c>
       <c r="L27" s="4"/>
-      <c r="M27" s="5"/>
-      <c r="N27" s="6"/>
-      <c r="O27" s="6"/>
-      <c r="P27" s="7"/>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="8"/>
-      <c r="T27" s="9"/>
-      <c r="U27" s="9"/>
-      <c r="V27" s="9"/>
-      <c r="W27" s="9"/>
-      <c r="X27" s="9"/>
-      <c r="Y27" s="9"/>
-      <c r="Z27" s="9"/>
-      <c r="AA27" s="9"/>
-      <c r="AB27" s="9"/>
-      <c r="AC27" s="9"/>
-      <c r="AD27" s="6"/>
-      <c r="AE27" s="6"/>
-      <c r="AF27" s="6"/>
-      <c r="AG27" s="6"/>
-      <c r="AH27" s="6"/>
-      <c r="AI27" s="6"/>
-      <c r="AJ27" s="6"/>
-      <c r="AK27" s="6"/>
-      <c r="AL27" s="6"/>
-      <c r="AM27" s="6"/>
-      <c r="AN27" s="9"/>
-      <c r="AO27" s="6"/>
+      <c r="M27" s="5">
+        <v>4991.9499999999998</v>
+      </c>
+      <c r="N27" s="6">
+        <v>52</v>
+      </c>
+      <c r="O27" s="6">
+        <v>29</v>
+      </c>
+      <c r="P27" s="7">
+        <v>5.0342773584905665</v>
+      </c>
+      <c r="Q27" s="8">
+        <v>18.509196551724138</v>
+      </c>
+      <c r="R27" s="8">
+        <v>5.9005964285714283</v>
+      </c>
+      <c r="S27" s="8">
+        <v>8</v>
+      </c>
+      <c r="T27" s="9">
+        <v>0.34482758620689657</v>
+      </c>
+      <c r="U27" s="9">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="V27" s="9">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="W27" s="9">
+        <v>0</v>
+      </c>
+      <c r="X27" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="Y27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="AB27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="9">
+        <v>0.17241379310344829</v>
+      </c>
+      <c r="AD27" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>7</v>
+      </c>
+      <c r="AF27" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK27" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL27" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="6">
+        <v>5</v>
+      </c>
+      <c r="AN27" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP27" s="4">
         <v>58</v>
       </c>
@@ -6176,7 +6570,7 @@
         <v>19561</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>51</v>
@@ -6206,35 +6600,93 @@
         <v>58</v>
       </c>
       <c r="L35" s="4"/>
-      <c r="M35" s="5"/>
-      <c r="N35" s="6"/>
-      <c r="O35" s="6"/>
-      <c r="P35" s="7"/>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="8"/>
-      <c r="S35" s="8"/>
-      <c r="T35" s="9"/>
-      <c r="U35" s="9"/>
-      <c r="V35" s="9"/>
-      <c r="W35" s="9"/>
-      <c r="X35" s="9"/>
-      <c r="Y35" s="9"/>
-      <c r="Z35" s="9"/>
-      <c r="AA35" s="9"/>
-      <c r="AB35" s="9"/>
-      <c r="AC35" s="9"/>
-      <c r="AD35" s="6"/>
-      <c r="AE35" s="6"/>
-      <c r="AF35" s="6"/>
-      <c r="AG35" s="6"/>
-      <c r="AH35" s="6"/>
-      <c r="AI35" s="6"/>
-      <c r="AJ35" s="6"/>
-      <c r="AK35" s="6"/>
-      <c r="AL35" s="6"/>
-      <c r="AM35" s="6"/>
-      <c r="AN35" s="9"/>
-      <c r="AO35" s="6"/>
+      <c r="M35" s="5">
+        <v>3266.4200000000001</v>
+      </c>
+      <c r="N35" s="6">
+        <v>31</v>
+      </c>
+      <c r="O35" s="6">
+        <v>20</v>
+      </c>
+      <c r="P35" s="7">
+        <v>13.183334482758621</v>
+      </c>
+      <c r="Q35" s="8">
+        <v>24.177500000000002</v>
+      </c>
+      <c r="R35" s="8">
+        <v>4.3805555555555555</v>
+      </c>
+      <c r="S35" s="8">
+        <v>7</v>
+      </c>
+      <c r="T35" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="U35" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="V35" s="9">
+        <v>0</v>
+      </c>
+      <c r="W35" s="9">
+        <v>0</v>
+      </c>
+      <c r="X35" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y35" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="AB35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE35" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH35" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK35" s="6">
+        <v>2</v>
+      </c>
+      <c r="AL35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM35" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN35" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP35" s="4">
         <v>58</v>
       </c>
@@ -6686,7 +7138,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>51</v>
@@ -6716,35 +7168,93 @@
         <v>58</v>
       </c>
       <c r="L39" s="4"/>
-      <c r="M39" s="5"/>
-      <c r="N39" s="6"/>
-      <c r="O39" s="6"/>
-      <c r="P39" s="7"/>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="8"/>
-      <c r="T39" s="9"/>
-      <c r="U39" s="9"/>
-      <c r="V39" s="9"/>
-      <c r="W39" s="9"/>
-      <c r="X39" s="9"/>
-      <c r="Y39" s="9"/>
-      <c r="Z39" s="9"/>
-      <c r="AA39" s="9"/>
-      <c r="AB39" s="9"/>
-      <c r="AC39" s="9"/>
-      <c r="AD39" s="6"/>
-      <c r="AE39" s="6"/>
-      <c r="AF39" s="6"/>
-      <c r="AG39" s="6"/>
-      <c r="AH39" s="6"/>
-      <c r="AI39" s="6"/>
-      <c r="AJ39" s="6"/>
-      <c r="AK39" s="6"/>
-      <c r="AL39" s="6"/>
-      <c r="AM39" s="6"/>
-      <c r="AN39" s="9"/>
-      <c r="AO39" s="6"/>
+      <c r="M39" s="5">
+        <v>5722.3299999999999</v>
+      </c>
+      <c r="N39" s="6">
+        <v>65</v>
+      </c>
+      <c r="O39" s="6">
+        <v>38</v>
+      </c>
+      <c r="P39" s="7">
+        <v>2.5966140625</v>
+      </c>
+      <c r="Q39" s="8">
+        <v>12.946052631578947</v>
+      </c>
+      <c r="R39" s="8">
+        <v>5.622668</v>
+      </c>
+      <c r="S39" s="8">
+        <v>8</v>
+      </c>
+      <c r="T39" s="9">
+        <v>0.71052631578947367</v>
+      </c>
+      <c r="U39" s="9">
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="V39" s="9">
+        <v>0.026315789473684209</v>
+      </c>
+      <c r="W39" s="9">
+        <v>0</v>
+      </c>
+      <c r="X39" s="9">
+        <v>0.078947368421052627</v>
+      </c>
+      <c r="Y39" s="9">
+        <v>0.10526315789473684</v>
+      </c>
+      <c r="Z39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA39" s="9">
+        <v>0.42105263157894735</v>
+      </c>
+      <c r="AB39" s="9">
+        <v>0.13157894736842105</v>
+      </c>
+      <c r="AC39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD39" s="6">
+        <v>29</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>24</v>
+      </c>
+      <c r="AF39" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH39" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI39" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK39" s="6">
+        <v>16</v>
+      </c>
+      <c r="AL39" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM39" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN39" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP39" s="4">
         <v>58</v>
       </c>
@@ -6942,7 +7452,7 @@
         <v>19578</v>
       </c>
       <c r="B41" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C41" s="4">
         <v>51</v>
@@ -6972,18 +7482,30 @@
         <v>58</v>
       </c>
       <c r="L41" s="4"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="6"/>
+      <c r="M41" s="5">
+        <v>4834.6599999999999</v>
+      </c>
+      <c r="N41" s="6">
+        <v>61</v>
+      </c>
       <c r="O41" s="6">
         <v>50</v>
       </c>
-      <c r="P41" s="7"/>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="8"/>
+      <c r="P41" s="7">
+        <v>2.7788883333333336</v>
+      </c>
+      <c r="Q41" s="8">
+        <v>15.131666000000001</v>
+      </c>
+      <c r="R41" s="8">
+        <v>6.7906249999999995</v>
+      </c>
       <c r="S41" s="8">
         <v>6</v>
       </c>
-      <c r="T41" s="9"/>
+      <c r="T41" s="9">
+        <v>0.64000000000000001</v>
+      </c>
       <c r="U41" s="9">
         <v>0.20000000000000001</v>
       </c>
@@ -7186,7 +7708,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>51</v>
@@ -7216,35 +7738,93 @@
         <v>58</v>
       </c>
       <c r="L43" s="4"/>
-      <c r="M43" s="5"/>
-      <c r="N43" s="6"/>
-      <c r="O43" s="6"/>
-      <c r="P43" s="7"/>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="8"/>
-      <c r="T43" s="9"/>
-      <c r="U43" s="9"/>
-      <c r="V43" s="9"/>
-      <c r="W43" s="9"/>
-      <c r="X43" s="9"/>
-      <c r="Y43" s="9"/>
-      <c r="Z43" s="9"/>
-      <c r="AA43" s="9"/>
-      <c r="AB43" s="9"/>
-      <c r="AC43" s="9"/>
-      <c r="AD43" s="6"/>
-      <c r="AE43" s="6"/>
-      <c r="AF43" s="6"/>
-      <c r="AG43" s="6"/>
-      <c r="AH43" s="6"/>
-      <c r="AI43" s="6"/>
-      <c r="AJ43" s="6"/>
-      <c r="AK43" s="6"/>
-      <c r="AL43" s="6"/>
-      <c r="AM43" s="6"/>
-      <c r="AN43" s="9"/>
-      <c r="AO43" s="6"/>
+      <c r="M43" s="5">
+        <v>5703.0699999999997</v>
+      </c>
+      <c r="N43" s="6">
+        <v>53</v>
+      </c>
+      <c r="O43" s="6">
+        <v>34</v>
+      </c>
+      <c r="P43" s="7">
+        <v>7.1644660377358491</v>
+      </c>
+      <c r="Q43" s="8">
+        <v>21.828281818181818</v>
+      </c>
+      <c r="R43" s="8">
+        <v>7.4868696969696966</v>
+      </c>
+      <c r="S43" s="8">
+        <v>7</v>
+      </c>
+      <c r="T43" s="9">
+        <v>0.12121212121212122</v>
+      </c>
+      <c r="U43" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="V43" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="W43" s="9">
+        <v>0</v>
+      </c>
+      <c r="X43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB43" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AC43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD43" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL43" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM43" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN43" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP43" s="4">
         <v>58</v>
       </c>
@@ -8066,7 +8646,7 @@
         <v>19600</v>
       </c>
       <c r="B49" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C49" s="4">
         <v>51</v>
@@ -8094,35 +8674,93 @@
         <v>58</v>
       </c>
       <c r="L49" s="4"/>
-      <c r="M49" s="5"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="6"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="8"/>
-      <c r="R49" s="8"/>
-      <c r="S49" s="8"/>
-      <c r="T49" s="9"/>
-      <c r="U49" s="9"/>
-      <c r="V49" s="9"/>
-      <c r="W49" s="9"/>
-      <c r="X49" s="9"/>
-      <c r="Y49" s="9"/>
-      <c r="Z49" s="9"/>
-      <c r="AA49" s="9"/>
-      <c r="AB49" s="9"/>
-      <c r="AC49" s="9"/>
-      <c r="AD49" s="6"/>
-      <c r="AE49" s="6"/>
-      <c r="AF49" s="6"/>
-      <c r="AG49" s="6"/>
-      <c r="AH49" s="6"/>
-      <c r="AI49" s="6"/>
-      <c r="AJ49" s="6"/>
-      <c r="AK49" s="6"/>
-      <c r="AL49" s="6"/>
-      <c r="AM49" s="6"/>
-      <c r="AN49" s="9"/>
-      <c r="AO49" s="6"/>
+      <c r="M49" s="5">
+        <v>4099.6599999999999</v>
+      </c>
+      <c r="N49" s="6">
+        <v>50</v>
+      </c>
+      <c r="O49" s="6">
+        <v>34</v>
+      </c>
+      <c r="P49" s="7">
+        <v>3.2907808510638294</v>
+      </c>
+      <c r="Q49" s="8">
+        <v>15.472058823529411</v>
+      </c>
+      <c r="R49" s="8">
+        <v>4.438726470588235</v>
+      </c>
+      <c r="S49" s="8">
+        <v>8</v>
+      </c>
+      <c r="T49" s="9">
+        <v>0.61764705882352944</v>
+      </c>
+      <c r="U49" s="9">
+        <v>0.17647058823529413</v>
+      </c>
+      <c r="V49" s="9">
+        <v>0</v>
+      </c>
+      <c r="W49" s="9">
+        <v>0</v>
+      </c>
+      <c r="X49" s="9">
+        <v>0.058823529411764705</v>
+      </c>
+      <c r="Y49" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AB49" s="9">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="AC49" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD49" s="6">
+        <v>7</v>
+      </c>
+      <c r="AE49" s="6">
+        <v>6</v>
+      </c>
+      <c r="AF49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH49" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK49" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL49" s="6">
+        <v>3</v>
+      </c>
+      <c r="AM49" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN49" s="9">
+        <v>0.029411764705882353</v>
+      </c>
+      <c r="AO49" s="6">
+        <v>1</v>
+      </c>
       <c t="s" r="AP49" s="4">
         <v>58</v>
       </c>
@@ -8552,7 +9190,9 @@
       <c r="N53" s="6">
         <v>35</v>
       </c>
-      <c r="O53" s="6"/>
+      <c r="O53" s="6">
+        <v>20</v>
+      </c>
       <c r="P53" s="7">
         <v>2.9104771428571428</v>
       </c>
@@ -8562,31 +9202,75 @@
       <c r="R53" s="8">
         <v>3.2041649999999997</v>
       </c>
-      <c r="S53" s="8"/>
+      <c r="S53" s="8">
+        <v>7</v>
+      </c>
       <c r="T53" s="9">
         <v>0.84999999999999998</v>
       </c>
-      <c r="U53" s="9"/>
-      <c r="V53" s="9"/>
-      <c r="W53" s="9"/>
-      <c r="X53" s="9"/>
-      <c r="Y53" s="9"/>
-      <c r="Z53" s="9"/>
-      <c r="AA53" s="9"/>
-      <c r="AB53" s="9"/>
-      <c r="AC53" s="9"/>
-      <c r="AD53" s="6"/>
-      <c r="AE53" s="6"/>
-      <c r="AF53" s="6"/>
-      <c r="AG53" s="6"/>
-      <c r="AH53" s="6"/>
-      <c r="AI53" s="6"/>
-      <c r="AJ53" s="6"/>
-      <c r="AK53" s="6"/>
-      <c r="AL53" s="6"/>
-      <c r="AM53" s="6"/>
-      <c r="AN53" s="9"/>
-      <c r="AO53" s="6"/>
+      <c r="U53" s="9">
+        <v>0</v>
+      </c>
+      <c r="V53" s="9">
+        <v>0</v>
+      </c>
+      <c r="W53" s="9">
+        <v>0</v>
+      </c>
+      <c r="X53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM53" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN53" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP53" s="4">
         <v>58</v>
       </c>
@@ -8784,7 +9468,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>51</v>
@@ -8814,35 +9498,93 @@
         <v>58</v>
       </c>
       <c r="L55" s="4"/>
-      <c r="M55" s="5"/>
-      <c r="N55" s="6"/>
-      <c r="O55" s="6"/>
-      <c r="P55" s="7"/>
-      <c r="Q55" s="8"/>
-      <c r="R55" s="8"/>
-      <c r="S55" s="8"/>
-      <c r="T55" s="9"/>
-      <c r="U55" s="9"/>
-      <c r="V55" s="9"/>
-      <c r="W55" s="9"/>
-      <c r="X55" s="9"/>
-      <c r="Y55" s="9"/>
-      <c r="Z55" s="9"/>
-      <c r="AA55" s="9"/>
-      <c r="AB55" s="9"/>
-      <c r="AC55" s="9"/>
-      <c r="AD55" s="6"/>
-      <c r="AE55" s="6"/>
-      <c r="AF55" s="6"/>
-      <c r="AG55" s="6"/>
-      <c r="AH55" s="6"/>
-      <c r="AI55" s="6"/>
-      <c r="AJ55" s="6"/>
-      <c r="AK55" s="6"/>
-      <c r="AL55" s="6"/>
-      <c r="AM55" s="6"/>
-      <c r="AN55" s="9"/>
-      <c r="AO55" s="6"/>
+      <c r="M55" s="5">
+        <v>4916.8999999999996</v>
+      </c>
+      <c r="N55" s="6">
+        <v>59</v>
+      </c>
+      <c r="O55" s="6">
+        <v>44</v>
+      </c>
+      <c r="P55" s="7">
+        <v>3.0197921874999998</v>
+      </c>
+      <c r="Q55" s="8">
+        <v>18.494318181818183</v>
+      </c>
+      <c r="R55" s="8">
+        <v>8.894960465116279</v>
+      </c>
+      <c r="S55" s="8">
+        <v>7</v>
+      </c>
+      <c r="T55" s="9">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="U55" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="V55" s="9">
+        <v>0</v>
+      </c>
+      <c r="W55" s="9">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="AB55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK55" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM55" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN55" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP55" s="4">
         <v>58</v>
       </c>
@@ -9195,7 +9937,7 @@
         <v>19618</v>
       </c>
       <c r="B58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C58" s="4">
         <v>51</v>
@@ -9225,14 +9967,26 @@
         <v>58</v>
       </c>
       <c r="L58" s="4"/>
-      <c r="M58" s="5"/>
-      <c r="N58" s="6"/>
+      <c r="M58" s="5">
+        <v>6474.2200000000003</v>
+      </c>
+      <c r="N58" s="6">
+        <v>75</v>
+      </c>
       <c r="O58" s="6"/>
-      <c r="P58" s="7"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
+      <c r="P58" s="7">
+        <v>2.8065732394366196</v>
+      </c>
+      <c r="Q58" s="8">
+        <v>14.096153846153847</v>
+      </c>
+      <c r="R58" s="8">
+        <v>4.1423076923076927</v>
+      </c>
       <c r="S58" s="8"/>
-      <c r="T58" s="9"/>
+      <c r="T58" s="9">
+        <v>0.71153846153846156</v>
+      </c>
       <c r="U58" s="9"/>
       <c r="V58" s="9"/>
       <c r="W58" s="9"/>
@@ -9451,7 +10205,7 @@
         <v>19623</v>
       </c>
       <c r="B60" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C60" s="4">
         <v>51</v>
@@ -9481,35 +10235,93 @@
         <v>58</v>
       </c>
       <c r="L60" s="4"/>
-      <c r="M60" s="5"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
-      <c r="P60" s="7"/>
-      <c r="Q60" s="8"/>
-      <c r="R60" s="8"/>
-      <c r="S60" s="8"/>
-      <c r="T60" s="9"/>
-      <c r="U60" s="9"/>
-      <c r="V60" s="9"/>
-      <c r="W60" s="9"/>
-      <c r="X60" s="9"/>
-      <c r="Y60" s="9"/>
-      <c r="Z60" s="9"/>
-      <c r="AA60" s="9"/>
-      <c r="AB60" s="9"/>
-      <c r="AC60" s="9"/>
-      <c r="AD60" s="6"/>
-      <c r="AE60" s="6"/>
-      <c r="AF60" s="6"/>
-      <c r="AG60" s="6"/>
-      <c r="AH60" s="6"/>
-      <c r="AI60" s="6"/>
-      <c r="AJ60" s="6"/>
-      <c r="AK60" s="6"/>
-      <c r="AL60" s="6"/>
-      <c r="AM60" s="6"/>
-      <c r="AN60" s="9"/>
-      <c r="AO60" s="6"/>
+      <c r="M60" s="5">
+        <v>2864.4000000000001</v>
+      </c>
+      <c r="N60" s="6">
+        <v>31</v>
+      </c>
+      <c r="O60" s="6">
+        <v>13</v>
+      </c>
+      <c r="P60" s="7">
+        <v>3.1919354838709677</v>
+      </c>
+      <c r="Q60" s="8">
+        <v>13.939746153846155</v>
+      </c>
+      <c r="R60" s="8">
+        <v>2.3294846153846156</v>
+      </c>
+      <c r="S60" s="8">
+        <v>8</v>
+      </c>
+      <c r="T60" s="9">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="U60" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="V60" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="W60" s="9">
+        <v>0</v>
+      </c>
+      <c r="X60" s="9">
+        <v>0.076923076923076927</v>
+      </c>
+      <c r="Y60" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE60" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH60" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM60" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN60" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO60" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP60" s="4">
         <v>58</v>
       </c>
@@ -11052,7 +11864,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>51</v>
@@ -11080,35 +11892,93 @@
         <v>58</v>
       </c>
       <c r="L71" s="4"/>
-      <c r="M71" s="5"/>
-      <c r="N71" s="6"/>
-      <c r="O71" s="6"/>
-      <c r="P71" s="7"/>
-      <c r="Q71" s="8"/>
-      <c r="R71" s="8"/>
-      <c r="S71" s="8"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
-      <c r="V71" s="9"/>
-      <c r="W71" s="9"/>
-      <c r="X71" s="9"/>
-      <c r="Y71" s="9"/>
-      <c r="Z71" s="9"/>
-      <c r="AA71" s="9"/>
-      <c r="AB71" s="9"/>
-      <c r="AC71" s="9"/>
-      <c r="AD71" s="6"/>
-      <c r="AE71" s="6"/>
-      <c r="AF71" s="6"/>
-      <c r="AG71" s="6"/>
-      <c r="AH71" s="6"/>
-      <c r="AI71" s="6"/>
-      <c r="AJ71" s="6"/>
-      <c r="AK71" s="6"/>
-      <c r="AL71" s="6"/>
-      <c r="AM71" s="6"/>
-      <c r="AN71" s="9"/>
-      <c r="AO71" s="6"/>
+      <c r="M71" s="5">
+        <v>5556.5900000000001</v>
+      </c>
+      <c r="N71" s="6">
+        <v>62</v>
+      </c>
+      <c r="O71" s="6">
+        <v>25</v>
+      </c>
+      <c r="P71" s="7">
+        <v>2.9592901639344258</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>16.655332000000001</v>
+      </c>
+      <c r="R71" s="8">
+        <v>5.5393320000000008</v>
+      </c>
+      <c r="S71" s="8">
+        <v>8</v>
+      </c>
+      <c r="T71" s="9">
+        <v>0.47999999999999998</v>
+      </c>
+      <c r="U71" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="V71" s="9">
+        <v>0</v>
+      </c>
+      <c r="W71" s="9">
+        <v>0</v>
+      </c>
+      <c r="X71" s="9">
+        <v>0.080000000000000002</v>
+      </c>
+      <c r="Y71" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH71" s="6">
+        <v>2</v>
+      </c>
+      <c r="AI71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM71" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN71" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO71" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP71" s="4">
         <v>58</v>
       </c>
@@ -11556,7 +12426,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>51</v>
@@ -11586,35 +12456,93 @@
         <v>58</v>
       </c>
       <c r="L75" s="4"/>
-      <c r="M75" s="5"/>
-      <c r="N75" s="6"/>
-      <c r="O75" s="6"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="8"/>
-      <c r="R75" s="8"/>
-      <c r="S75" s="8"/>
-      <c r="T75" s="9"/>
-      <c r="U75" s="9"/>
-      <c r="V75" s="9"/>
-      <c r="W75" s="9"/>
-      <c r="X75" s="9"/>
-      <c r="Y75" s="9"/>
-      <c r="Z75" s="9"/>
-      <c r="AA75" s="9"/>
-      <c r="AB75" s="9"/>
-      <c r="AC75" s="9"/>
-      <c r="AD75" s="6"/>
-      <c r="AE75" s="6"/>
-      <c r="AF75" s="6"/>
-      <c r="AG75" s="6"/>
-      <c r="AH75" s="6"/>
-      <c r="AI75" s="6"/>
-      <c r="AJ75" s="6"/>
-      <c r="AK75" s="6"/>
-      <c r="AL75" s="6"/>
-      <c r="AM75" s="6"/>
-      <c r="AN75" s="9"/>
-      <c r="AO75" s="6"/>
+      <c r="M75" s="5">
+        <v>4030.9099999999999</v>
+      </c>
+      <c r="N75" s="6">
+        <v>42</v>
+      </c>
+      <c r="O75" s="6">
+        <v>18</v>
+      </c>
+      <c r="P75" s="7">
+        <v>5.3158738095238096</v>
+      </c>
+      <c r="Q75" s="8">
+        <v>16.980555555555554</v>
+      </c>
+      <c r="R75" s="8">
+        <v>5.3379611111111105</v>
+      </c>
+      <c r="S75" s="8">
+        <v>7</v>
+      </c>
+      <c r="T75" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="U75" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="V75" s="9">
+        <v>0</v>
+      </c>
+      <c r="W75" s="9">
+        <v>0</v>
+      </c>
+      <c r="X75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB75" s="9">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AC75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL75" s="6">
+        <v>4</v>
+      </c>
+      <c r="AM75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN75" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO75" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP75" s="4">
         <v>58</v>
       </c>
@@ -12062,7 +12990,7 @@
         <v>19671</v>
       </c>
       <c r="B79" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C79" s="4">
         <v>51</v>
@@ -12092,35 +13020,93 @@
         <v>58</v>
       </c>
       <c r="L79" s="4"/>
-      <c r="M79" s="5"/>
-      <c r="N79" s="6"/>
-      <c r="O79" s="6"/>
-      <c r="P79" s="7"/>
-      <c r="Q79" s="8"/>
-      <c r="R79" s="8"/>
-      <c r="S79" s="8"/>
-      <c r="T79" s="9"/>
-      <c r="U79" s="9"/>
-      <c r="V79" s="9"/>
-      <c r="W79" s="9"/>
-      <c r="X79" s="9"/>
-      <c r="Y79" s="9"/>
-      <c r="Z79" s="9"/>
-      <c r="AA79" s="9"/>
-      <c r="AB79" s="9"/>
-      <c r="AC79" s="9"/>
-      <c r="AD79" s="6"/>
-      <c r="AE79" s="6"/>
-      <c r="AF79" s="6"/>
-      <c r="AG79" s="6"/>
-      <c r="AH79" s="6"/>
-      <c r="AI79" s="6"/>
-      <c r="AJ79" s="6"/>
-      <c r="AK79" s="6"/>
-      <c r="AL79" s="6"/>
-      <c r="AM79" s="6"/>
-      <c r="AN79" s="9"/>
-      <c r="AO79" s="6"/>
+      <c r="M79" s="5">
+        <v>6626.5500000000002</v>
+      </c>
+      <c r="N79" s="6">
+        <v>65</v>
+      </c>
+      <c r="O79" s="6">
+        <v>29</v>
+      </c>
+      <c r="P79" s="7">
+        <v>6.9835892307692307</v>
+      </c>
+      <c r="Q79" s="8">
+        <v>26.472989655172412</v>
+      </c>
+      <c r="R79" s="8">
+        <v>13.084482758620689</v>
+      </c>
+      <c r="S79" s="8">
+        <v>7</v>
+      </c>
+      <c r="T79" s="9">
+        <v>0.068965517241379309</v>
+      </c>
+      <c r="U79" s="9">
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="V79" s="9">
+        <v>0</v>
+      </c>
+      <c r="W79" s="9">
+        <v>0</v>
+      </c>
+      <c r="X79" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB79" s="9">
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="AC79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="6">
+        <v>8</v>
+      </c>
+      <c r="AE79" s="6">
+        <v>8</v>
+      </c>
+      <c r="AF79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL79" s="6">
+        <v>8</v>
+      </c>
+      <c r="AM79" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN79" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO79" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP79" s="4">
         <v>58</v>
       </c>
@@ -13609,7 +14595,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>51</v>
@@ -13639,35 +14625,93 @@
         <v>58</v>
       </c>
       <c r="L90" s="4"/>
-      <c r="M90" s="5"/>
-      <c r="N90" s="6"/>
-      <c r="O90" s="6"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="8"/>
-      <c r="R90" s="8"/>
-      <c r="S90" s="8"/>
-      <c r="T90" s="9"/>
-      <c r="U90" s="9"/>
-      <c r="V90" s="9"/>
-      <c r="W90" s="9"/>
-      <c r="X90" s="9"/>
-      <c r="Y90" s="9"/>
-      <c r="Z90" s="9"/>
-      <c r="AA90" s="9"/>
-      <c r="AB90" s="9"/>
-      <c r="AC90" s="9"/>
-      <c r="AD90" s="6"/>
-      <c r="AE90" s="6"/>
-      <c r="AF90" s="6"/>
-      <c r="AG90" s="6"/>
-      <c r="AH90" s="6"/>
-      <c r="AI90" s="6"/>
-      <c r="AJ90" s="6"/>
-      <c r="AK90" s="6"/>
-      <c r="AL90" s="6"/>
-      <c r="AM90" s="6"/>
-      <c r="AN90" s="9"/>
-      <c r="AO90" s="6"/>
+      <c r="M90" s="5">
+        <v>4447.1300000000001</v>
+      </c>
+      <c r="N90" s="6">
+        <v>52</v>
+      </c>
+      <c r="O90" s="6">
+        <v>31</v>
+      </c>
+      <c r="P90" s="7">
+        <v>4.9066660000000004</v>
+      </c>
+      <c r="Q90" s="8">
+        <v>28.677419354838708</v>
+      </c>
+      <c r="R90" s="8">
+        <v>18.616667741935483</v>
+      </c>
+      <c r="S90" s="8">
+        <v>7</v>
+      </c>
+      <c r="T90" s="9">
+        <v>0.096774193548387094</v>
+      </c>
+      <c r="U90" s="9">
+        <v>0.4838709677419355</v>
+      </c>
+      <c r="V90" s="9">
+        <v>0.032258064516129031</v>
+      </c>
+      <c r="W90" s="9">
+        <v>0</v>
+      </c>
+      <c r="X90" s="9">
+        <v>0.12903225806451613</v>
+      </c>
+      <c r="Y90" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="9">
+        <v>0.064516129032258063</v>
+      </c>
+      <c r="AC90" s="9">
+        <v>0.32258064516129031</v>
+      </c>
+      <c r="AD90" s="6">
+        <v>17</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF90" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH90" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK90" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL90" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM90" s="6">
+        <v>10</v>
+      </c>
+      <c r="AN90" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO90" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP90" s="4">
         <v>58</v>
       </c>
@@ -16348,7 +17392,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>51</v>
@@ -16376,35 +17420,93 @@
         <v>58</v>
       </c>
       <c r="L109" s="4"/>
-      <c r="M109" s="5"/>
-      <c r="N109" s="6"/>
-      <c r="O109" s="6"/>
-      <c r="P109" s="7"/>
-      <c r="Q109" s="8"/>
-      <c r="R109" s="8"/>
-      <c r="S109" s="8"/>
-      <c r="T109" s="9"/>
-      <c r="U109" s="9"/>
-      <c r="V109" s="9"/>
-      <c r="W109" s="9"/>
-      <c r="X109" s="9"/>
-      <c r="Y109" s="9"/>
-      <c r="Z109" s="9"/>
-      <c r="AA109" s="9"/>
-      <c r="AB109" s="9"/>
-      <c r="AC109" s="9"/>
-      <c r="AD109" s="6"/>
-      <c r="AE109" s="6"/>
-      <c r="AF109" s="6"/>
-      <c r="AG109" s="6"/>
-      <c r="AH109" s="6"/>
-      <c r="AI109" s="6"/>
-      <c r="AJ109" s="6"/>
-      <c r="AK109" s="6"/>
-      <c r="AL109" s="6"/>
-      <c r="AM109" s="6"/>
-      <c r="AN109" s="9"/>
-      <c r="AO109" s="6"/>
+      <c r="M109" s="5">
+        <v>6606.1000000000004</v>
+      </c>
+      <c r="N109" s="6">
+        <v>65</v>
+      </c>
+      <c r="O109" s="6">
+        <v>15</v>
+      </c>
+      <c r="P109" s="7">
+        <v>4.9974742424242429</v>
+      </c>
+      <c r="Q109" s="8">
+        <v>20.692220000000002</v>
+      </c>
+      <c r="R109" s="8">
+        <v>7.808886666666667</v>
+      </c>
+      <c r="S109" s="8">
+        <v>8</v>
+      </c>
+      <c r="T109" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U109" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V109" s="9">
+        <v>0</v>
+      </c>
+      <c r="W109" s="9">
+        <v>0</v>
+      </c>
+      <c r="X109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC109" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AD109" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL109" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM109" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN109" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO109" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP109" s="4">
         <v>58</v>
       </c>
@@ -20377,7 +21479,9 @@
       <c r="N136" s="6">
         <v>34</v>
       </c>
-      <c r="O136" s="6"/>
+      <c r="O136" s="6">
+        <v>21</v>
+      </c>
       <c r="P136" s="7">
         <v>7.3742857142857146</v>
       </c>
@@ -20387,31 +21491,75 @@
       <c r="R136" s="8">
         <v>6.7150809523809514</v>
       </c>
-      <c r="S136" s="8"/>
+      <c r="S136" s="8">
+        <v>7</v>
+      </c>
       <c r="T136" s="9">
         <v>0.19047619047619047</v>
       </c>
-      <c r="U136" s="9"/>
-      <c r="V136" s="9"/>
-      <c r="W136" s="9"/>
-      <c r="X136" s="9"/>
-      <c r="Y136" s="9"/>
-      <c r="Z136" s="9"/>
-      <c r="AA136" s="9"/>
-      <c r="AB136" s="9"/>
-      <c r="AC136" s="9"/>
-      <c r="AD136" s="6"/>
-      <c r="AE136" s="6"/>
-      <c r="AF136" s="6"/>
-      <c r="AG136" s="6"/>
-      <c r="AH136" s="6"/>
-      <c r="AI136" s="6"/>
-      <c r="AJ136" s="6"/>
-      <c r="AK136" s="6"/>
-      <c r="AL136" s="6"/>
-      <c r="AM136" s="6"/>
-      <c r="AN136" s="9"/>
-      <c r="AO136" s="6"/>
+      <c r="U136" s="9">
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="V136" s="9">
+        <v>0</v>
+      </c>
+      <c r="W136" s="9">
+        <v>0</v>
+      </c>
+      <c r="X136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y136" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA136" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AB136" s="9">
+        <v>0.047619047619047616</v>
+      </c>
+      <c r="AC136" s="9">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AD136" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE136" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ136" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK136" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL136" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM136" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN136" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO136" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP136" s="4">
         <v>58</v>
       </c>
@@ -20607,7 +21755,7 @@
         <v>19788</v>
       </c>
       <c r="B138" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C138" s="4">
         <v>51</v>
@@ -20635,35 +21783,93 @@
         <v>58</v>
       </c>
       <c r="L138" s="4"/>
-      <c r="M138" s="5"/>
-      <c r="N138" s="6"/>
-      <c r="O138" s="6"/>
-      <c r="P138" s="7"/>
-      <c r="Q138" s="8"/>
-      <c r="R138" s="8"/>
-      <c r="S138" s="8"/>
-      <c r="T138" s="9"/>
-      <c r="U138" s="9"/>
-      <c r="V138" s="9"/>
-      <c r="W138" s="9"/>
-      <c r="X138" s="9"/>
-      <c r="Y138" s="9"/>
-      <c r="Z138" s="9"/>
-      <c r="AA138" s="9"/>
-      <c r="AB138" s="9"/>
-      <c r="AC138" s="9"/>
-      <c r="AD138" s="6"/>
-      <c r="AE138" s="6"/>
-      <c r="AF138" s="6"/>
-      <c r="AG138" s="6"/>
-      <c r="AH138" s="6"/>
-      <c r="AI138" s="6"/>
-      <c r="AJ138" s="6"/>
-      <c r="AK138" s="6"/>
-      <c r="AL138" s="6"/>
-      <c r="AM138" s="6"/>
-      <c r="AN138" s="9"/>
-      <c r="AO138" s="6"/>
+      <c r="M138" s="5">
+        <v>14484.02</v>
+      </c>
+      <c r="N138" s="6">
+        <v>132</v>
+      </c>
+      <c r="O138" s="6">
+        <v>95</v>
+      </c>
+      <c r="P138" s="7">
+        <v>4.9892857142857139</v>
+      </c>
+      <c r="Q138" s="8">
+        <v>18.395965263157894</v>
+      </c>
+      <c r="R138" s="8">
+        <v>6.9005434782608699</v>
+      </c>
+      <c r="S138" s="8">
+        <v>7</v>
+      </c>
+      <c r="T138" s="9">
+        <v>0.18947368421052632</v>
+      </c>
+      <c r="U138" s="9">
+        <v>0.052631578947368418</v>
+      </c>
+      <c r="V138" s="9">
+        <v>0.010526315789473684</v>
+      </c>
+      <c r="W138" s="9">
+        <v>0.021052631578000001</v>
+      </c>
+      <c r="X138" s="9">
+        <v>0.031578947368421054</v>
+      </c>
+      <c r="Y138" s="9">
+        <v>0.031578947368421054</v>
+      </c>
+      <c r="Z138" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA138" s="9">
+        <v>0.031578947368421054</v>
+      </c>
+      <c r="AB138" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC138" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD138" s="6">
+        <v>10</v>
+      </c>
+      <c r="AE138" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF138" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG138" s="6">
+        <v>2</v>
+      </c>
+      <c r="AH138" s="6">
+        <v>3</v>
+      </c>
+      <c r="AI138" s="6">
+        <v>3</v>
+      </c>
+      <c r="AJ138" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK138" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL138" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM138" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN138" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO138" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP138" s="4">
         <v>58</v>
       </c>
@@ -24017,7 +25223,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>51</v>
@@ -24047,35 +25253,93 @@
         <v>58</v>
       </c>
       <c r="L162" s="4"/>
-      <c r="M162" s="5"/>
-      <c r="N162" s="6"/>
-      <c r="O162" s="6"/>
-      <c r="P162" s="7"/>
-      <c r="Q162" s="8"/>
-      <c r="R162" s="8"/>
-      <c r="S162" s="8"/>
-      <c r="T162" s="9"/>
-      <c r="U162" s="9"/>
-      <c r="V162" s="9"/>
-      <c r="W162" s="9"/>
-      <c r="X162" s="9"/>
-      <c r="Y162" s="9"/>
-      <c r="Z162" s="9"/>
-      <c r="AA162" s="9"/>
-      <c r="AB162" s="9"/>
-      <c r="AC162" s="9"/>
-      <c r="AD162" s="6"/>
-      <c r="AE162" s="6"/>
-      <c r="AF162" s="6"/>
-      <c r="AG162" s="6"/>
-      <c r="AH162" s="6"/>
-      <c r="AI162" s="6"/>
-      <c r="AJ162" s="6"/>
-      <c r="AK162" s="6"/>
-      <c r="AL162" s="6"/>
-      <c r="AM162" s="6"/>
-      <c r="AN162" s="9"/>
-      <c r="AO162" s="6"/>
+      <c r="M162" s="5">
+        <v>4879.4300000000003</v>
+      </c>
+      <c r="N162" s="6">
+        <v>50</v>
+      </c>
+      <c r="O162" s="6">
+        <v>24</v>
+      </c>
+      <c r="P162" s="7">
+        <v>7.4937499999999995</v>
+      </c>
+      <c r="Q162" s="8">
+        <v>19.559029166666665</v>
+      </c>
+      <c r="R162" s="8">
+        <v>3.4493041666666664</v>
+      </c>
+      <c r="S162" s="8">
+        <v>8</v>
+      </c>
+      <c r="T162" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="U162" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V162" s="9">
+        <v>0</v>
+      </c>
+      <c r="W162" s="9">
+        <v>0</v>
+      </c>
+      <c r="X162" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="Y162" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z162" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AA162" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AB162" s="9">
+        <v>0.041666666666666664</v>
+      </c>
+      <c r="AC162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD162" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>4</v>
+      </c>
+      <c r="AF162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AK162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL162" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM162" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN162" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO162" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP162" s="4">
         <v>58</v>
       </c>
@@ -25471,7 +26735,7 @@
         <v>19890</v>
       </c>
       <c r="B172" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C172" s="4">
         <v>51</v>
@@ -25501,35 +26765,93 @@
         <v>58</v>
       </c>
       <c r="L172" s="4"/>
-      <c r="M172" s="5"/>
-      <c r="N172" s="6"/>
-      <c r="O172" s="6"/>
-      <c r="P172" s="7"/>
-      <c r="Q172" s="8"/>
-      <c r="R172" s="8"/>
-      <c r="S172" s="8"/>
-      <c r="T172" s="9"/>
-      <c r="U172" s="9"/>
-      <c r="V172" s="9"/>
-      <c r="W172" s="9"/>
-      <c r="X172" s="9"/>
-      <c r="Y172" s="9"/>
-      <c r="Z172" s="9"/>
-      <c r="AA172" s="9"/>
-      <c r="AB172" s="9"/>
-      <c r="AC172" s="9"/>
-      <c r="AD172" s="6"/>
-      <c r="AE172" s="6"/>
-      <c r="AF172" s="6"/>
-      <c r="AG172" s="6"/>
-      <c r="AH172" s="6"/>
-      <c r="AI172" s="6"/>
-      <c r="AJ172" s="6"/>
-      <c r="AK172" s="6"/>
-      <c r="AL172" s="6"/>
-      <c r="AM172" s="6"/>
-      <c r="AN172" s="9"/>
-      <c r="AO172" s="6"/>
+      <c r="M172" s="5">
+        <v>2115.2399999999998</v>
+      </c>
+      <c r="N172" s="6">
+        <v>24</v>
+      </c>
+      <c r="O172" s="6">
+        <v>20</v>
+      </c>
+      <c r="P172" s="7">
+        <v>5.568117391304348</v>
+      </c>
+      <c r="Q172" s="8">
+        <v>19.141665</v>
+      </c>
+      <c r="R172" s="8">
+        <v>6.2625000000000002</v>
+      </c>
+      <c r="S172" s="8">
+        <v>7</v>
+      </c>
+      <c r="T172" s="9">
+        <v>0.10000000000000001</v>
+      </c>
+      <c r="U172" s="9">
+        <v>0.14999999999999999</v>
+      </c>
+      <c r="V172" s="9">
+        <v>0</v>
+      </c>
+      <c r="W172" s="9">
+        <v>0</v>
+      </c>
+      <c r="X172" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y172" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA172" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AB172" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="AC172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD172" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE172" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL172" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM172" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN172" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO172" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP172" s="4">
         <v>58</v>
       </c>
@@ -26039,7 +27361,7 @@
         <v>19898</v>
       </c>
       <c r="B176" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C176" s="4">
         <v>51</v>
@@ -26067,35 +27389,93 @@
         <v>58</v>
       </c>
       <c r="L176" s="4"/>
-      <c r="M176" s="5"/>
-      <c r="N176" s="6"/>
-      <c r="O176" s="6"/>
-      <c r="P176" s="7"/>
-      <c r="Q176" s="8"/>
-      <c r="R176" s="8"/>
-      <c r="S176" s="8"/>
-      <c r="T176" s="9"/>
-      <c r="U176" s="9"/>
-      <c r="V176" s="9"/>
-      <c r="W176" s="9"/>
-      <c r="X176" s="9"/>
-      <c r="Y176" s="9"/>
-      <c r="Z176" s="9"/>
-      <c r="AA176" s="9"/>
-      <c r="AB176" s="9"/>
-      <c r="AC176" s="9"/>
-      <c r="AD176" s="6"/>
-      <c r="AE176" s="6"/>
-      <c r="AF176" s="6"/>
-      <c r="AG176" s="6"/>
-      <c r="AH176" s="6"/>
-      <c r="AI176" s="6"/>
-      <c r="AJ176" s="6"/>
-      <c r="AK176" s="6"/>
-      <c r="AL176" s="6"/>
-      <c r="AM176" s="6"/>
-      <c r="AN176" s="9"/>
-      <c r="AO176" s="6"/>
+      <c r="M176" s="5">
+        <v>3484.2399999999998</v>
+      </c>
+      <c r="N176" s="6">
+        <v>38</v>
+      </c>
+      <c r="O176" s="6">
+        <v>25</v>
+      </c>
+      <c r="P176" s="7">
+        <v>3.6598282051282056</v>
+      </c>
+      <c r="Q176" s="8">
+        <v>24.254668000000002</v>
+      </c>
+      <c r="R176" s="8">
+        <v>13.888</v>
+      </c>
+      <c r="S176" s="8">
+        <v>7</v>
+      </c>
+      <c r="T176" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="U176" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="V176" s="9">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="W176" s="9">
+        <v>0</v>
+      </c>
+      <c r="X176" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y176" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD176" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE176" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF176" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN176" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO176" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP176" s="4">
         <v>58</v>
       </c>
@@ -26557,7 +27937,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>51</v>
@@ -26587,35 +27967,93 @@
         <v>58</v>
       </c>
       <c r="L180" s="4"/>
-      <c r="M180" s="5"/>
-      <c r="N180" s="6"/>
-      <c r="O180" s="6"/>
-      <c r="P180" s="7"/>
-      <c r="Q180" s="8"/>
-      <c r="R180" s="8"/>
-      <c r="S180" s="8"/>
-      <c r="T180" s="9"/>
-      <c r="U180" s="9"/>
-      <c r="V180" s="9"/>
-      <c r="W180" s="9"/>
-      <c r="X180" s="9"/>
-      <c r="Y180" s="9"/>
-      <c r="Z180" s="9"/>
-      <c r="AA180" s="9"/>
-      <c r="AB180" s="9"/>
-      <c r="AC180" s="9"/>
-      <c r="AD180" s="6"/>
-      <c r="AE180" s="6"/>
-      <c r="AF180" s="6"/>
-      <c r="AG180" s="6"/>
-      <c r="AH180" s="6"/>
-      <c r="AI180" s="6"/>
-      <c r="AJ180" s="6"/>
-      <c r="AK180" s="6"/>
-      <c r="AL180" s="6"/>
-      <c r="AM180" s="6"/>
-      <c r="AN180" s="9"/>
-      <c r="AO180" s="6"/>
+      <c r="M180" s="5">
+        <v>2010.9000000000001</v>
+      </c>
+      <c r="N180" s="6">
+        <v>24</v>
+      </c>
+      <c r="O180" s="6">
+        <v>7</v>
+      </c>
+      <c r="P180" s="7">
+        <v>5.1536217391304344</v>
+      </c>
+      <c r="Q180" s="8">
+        <v>45.523814285714288</v>
+      </c>
+      <c r="R180" s="8">
+        <v>32.661899999999996</v>
+      </c>
+      <c r="S180" s="8">
+        <v>8</v>
+      </c>
+      <c r="T180" s="9">
+        <v>0</v>
+      </c>
+      <c r="U180" s="9">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="V180" s="9">
+        <v>0</v>
+      </c>
+      <c r="W180" s="9">
+        <v>0</v>
+      </c>
+      <c r="X180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y180" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB180" s="9">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="AC180" s="9">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AD180" s="6">
+        <v>5</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK180" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL180" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM180" s="6">
+        <v>4</v>
+      </c>
+      <c r="AN180" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO180" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP180" s="4">
         <v>58</v>
       </c>
@@ -26656,7 +28094,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>51</v>
@@ -26686,35 +28124,93 @@
         <v>58</v>
       </c>
       <c r="L181" s="4"/>
-      <c r="M181" s="5"/>
-      <c r="N181" s="6"/>
-      <c r="O181" s="6"/>
-      <c r="P181" s="7"/>
-      <c r="Q181" s="8"/>
-      <c r="R181" s="8"/>
-      <c r="S181" s="8"/>
-      <c r="T181" s="9"/>
-      <c r="U181" s="9"/>
-      <c r="V181" s="9"/>
-      <c r="W181" s="9"/>
-      <c r="X181" s="9"/>
-      <c r="Y181" s="9"/>
-      <c r="Z181" s="9"/>
-      <c r="AA181" s="9"/>
-      <c r="AB181" s="9"/>
-      <c r="AC181" s="9"/>
-      <c r="AD181" s="6"/>
-      <c r="AE181" s="6"/>
-      <c r="AF181" s="6"/>
-      <c r="AG181" s="6"/>
-      <c r="AH181" s="6"/>
-      <c r="AI181" s="6"/>
-      <c r="AJ181" s="6"/>
-      <c r="AK181" s="6"/>
-      <c r="AL181" s="6"/>
-      <c r="AM181" s="6"/>
-      <c r="AN181" s="9"/>
-      <c r="AO181" s="6"/>
+      <c r="M181" s="5">
+        <v>2879.1999999999998</v>
+      </c>
+      <c r="N181" s="6">
+        <v>31</v>
+      </c>
+      <c r="O181" s="6">
+        <v>17</v>
+      </c>
+      <c r="P181" s="7">
+        <v>3.0472233333333336</v>
+      </c>
+      <c r="Q181" s="8">
+        <v>10.31458125</v>
+      </c>
+      <c r="R181" s="8">
+        <v>3.3963000000000001</v>
+      </c>
+      <c r="S181" s="8">
+        <v>8</v>
+      </c>
+      <c r="T181" s="9">
+        <v>0.875</v>
+      </c>
+      <c r="U181" s="9">
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="V181" s="9">
+        <v>0</v>
+      </c>
+      <c r="W181" s="9">
+        <v>0</v>
+      </c>
+      <c r="X181" s="9">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="Y181" s="9">
+        <v>0.23529411764705882</v>
+      </c>
+      <c r="Z181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="9">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="AB181" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AC181" s="9">
+        <v>0.11764705882352941</v>
+      </c>
+      <c r="AD181" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>10</v>
+      </c>
+      <c r="AF181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH181" s="6">
+        <v>4</v>
+      </c>
+      <c r="AI181" s="6">
+        <v>4</v>
+      </c>
+      <c r="AJ181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK181" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM181" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN181" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO181" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP181" s="4">
         <v>58</v>
       </c>
@@ -27482,7 +28978,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>51</v>
@@ -27512,35 +29008,93 @@
         <v>58</v>
       </c>
       <c r="L187" s="4"/>
-      <c r="M187" s="5"/>
-      <c r="N187" s="6"/>
-      <c r="O187" s="6"/>
-      <c r="P187" s="7"/>
-      <c r="Q187" s="8"/>
-      <c r="R187" s="8"/>
-      <c r="S187" s="8"/>
-      <c r="T187" s="9"/>
-      <c r="U187" s="9"/>
-      <c r="V187" s="9"/>
-      <c r="W187" s="9"/>
-      <c r="X187" s="9"/>
-      <c r="Y187" s="9"/>
-      <c r="Z187" s="9"/>
-      <c r="AA187" s="9"/>
-      <c r="AB187" s="9"/>
-      <c r="AC187" s="9"/>
-      <c r="AD187" s="6"/>
-      <c r="AE187" s="6"/>
-      <c r="AF187" s="6"/>
-      <c r="AG187" s="6"/>
-      <c r="AH187" s="6"/>
-      <c r="AI187" s="6"/>
-      <c r="AJ187" s="6"/>
-      <c r="AK187" s="6"/>
-      <c r="AL187" s="6"/>
-      <c r="AM187" s="6"/>
-      <c r="AN187" s="9"/>
-      <c r="AO187" s="6"/>
+      <c r="M187" s="5">
+        <v>1151.45</v>
+      </c>
+      <c r="N187" s="6">
+        <v>17</v>
+      </c>
+      <c r="O187" s="6">
+        <v>12</v>
+      </c>
+      <c r="P187" s="7">
+        <v>9.1029411764705888</v>
+      </c>
+      <c r="Q187" s="8">
+        <v>27.875</v>
+      </c>
+      <c r="R187" s="8">
+        <v>11.879166666666668</v>
+      </c>
+      <c r="S187" s="8">
+        <v>7</v>
+      </c>
+      <c r="T187" s="9">
+        <v>0</v>
+      </c>
+      <c r="U187" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="V187" s="9">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="W187" s="9">
+        <v>0</v>
+      </c>
+      <c r="X187" s="9">
+        <v>0.083333333333333329</v>
+      </c>
+      <c r="Y187" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD187" s="6">
+        <v>3</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF187" s="6">
+        <v>2</v>
+      </c>
+      <c r="AG187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH187" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM187" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN187" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO187" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP187" s="4">
         <v>58</v>
       </c>
@@ -27738,7 +29292,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>51</v>
@@ -27768,35 +29322,93 @@
         <v>58</v>
       </c>
       <c r="L189" s="4"/>
-      <c r="M189" s="5"/>
-      <c r="N189" s="6"/>
-      <c r="O189" s="6"/>
-      <c r="P189" s="7"/>
-      <c r="Q189" s="8"/>
-      <c r="R189" s="8"/>
-      <c r="S189" s="8"/>
-      <c r="T189" s="9"/>
-      <c r="U189" s="9"/>
-      <c r="V189" s="9"/>
-      <c r="W189" s="9"/>
-      <c r="X189" s="9"/>
-      <c r="Y189" s="9"/>
-      <c r="Z189" s="9"/>
-      <c r="AA189" s="9"/>
-      <c r="AB189" s="9"/>
-      <c r="AC189" s="9"/>
-      <c r="AD189" s="6"/>
-      <c r="AE189" s="6"/>
-      <c r="AF189" s="6"/>
-      <c r="AG189" s="6"/>
-      <c r="AH189" s="6"/>
-      <c r="AI189" s="6"/>
-      <c r="AJ189" s="6"/>
-      <c r="AK189" s="6"/>
-      <c r="AL189" s="6"/>
-      <c r="AM189" s="6"/>
-      <c r="AN189" s="9"/>
-      <c r="AO189" s="6"/>
+      <c r="M189" s="5">
+        <v>3247.3099999999999</v>
+      </c>
+      <c r="N189" s="6">
+        <v>48</v>
+      </c>
+      <c r="O189" s="6">
+        <v>41</v>
+      </c>
+      <c r="P189" s="7">
+        <v>4.5746520833333335</v>
+      </c>
+      <c r="Q189" s="8">
+        <v>23.376829268292685</v>
+      </c>
+      <c r="R189" s="8">
+        <v>11.722763414634146</v>
+      </c>
+      <c r="S189" s="8">
+        <v>7</v>
+      </c>
+      <c r="T189" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="U189" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="V189" s="9">
+        <v>0</v>
+      </c>
+      <c r="W189" s="9">
+        <v>0</v>
+      </c>
+      <c r="X189" s="9">
+        <v>0.024390243902439025</v>
+      </c>
+      <c r="Y189" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC189" s="9">
+        <v>0.073170731707317069</v>
+      </c>
+      <c r="AD189" s="6">
+        <v>4</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>3</v>
+      </c>
+      <c r="AF189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH189" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL189" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM189" s="6">
+        <v>3</v>
+      </c>
+      <c r="AN189" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO189" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP189" s="4">
         <v>58</v>
       </c>
@@ -27837,7 +29449,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>51</v>
@@ -27867,35 +29479,93 @@
         <v>58</v>
       </c>
       <c r="L190" s="4"/>
-      <c r="M190" s="5"/>
-      <c r="N190" s="6"/>
-      <c r="O190" s="6"/>
-      <c r="P190" s="7"/>
-      <c r="Q190" s="8"/>
-      <c r="R190" s="8"/>
-      <c r="S190" s="8"/>
-      <c r="T190" s="9"/>
-      <c r="U190" s="9"/>
-      <c r="V190" s="9"/>
-      <c r="W190" s="9"/>
-      <c r="X190" s="9"/>
-      <c r="Y190" s="9"/>
-      <c r="Z190" s="9"/>
-      <c r="AA190" s="9"/>
-      <c r="AB190" s="9"/>
-      <c r="AC190" s="9"/>
-      <c r="AD190" s="6"/>
-      <c r="AE190" s="6"/>
-      <c r="AF190" s="6"/>
-      <c r="AG190" s="6"/>
-      <c r="AH190" s="6"/>
-      <c r="AI190" s="6"/>
-      <c r="AJ190" s="6"/>
-      <c r="AK190" s="6"/>
-      <c r="AL190" s="6"/>
-      <c r="AM190" s="6"/>
-      <c r="AN190" s="9"/>
-      <c r="AO190" s="6"/>
+      <c r="M190" s="5">
+        <v>3058.8200000000002</v>
+      </c>
+      <c r="N190" s="6">
+        <v>34</v>
+      </c>
+      <c r="O190" s="6">
+        <v>8</v>
+      </c>
+      <c r="P190" s="7">
+        <v>3.5284323529411767</v>
+      </c>
+      <c r="Q190" s="8">
+        <v>16.358337500000001</v>
+      </c>
+      <c r="R190" s="8">
+        <v>5.5250000000000004</v>
+      </c>
+      <c r="S190" s="8">
+        <v>7</v>
+      </c>
+      <c r="T190" s="9">
+        <v>0.375</v>
+      </c>
+      <c r="U190" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="V190" s="9">
+        <v>0</v>
+      </c>
+      <c r="W190" s="9">
+        <v>0</v>
+      </c>
+      <c r="X190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y190" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB190" s="9">
+        <v>0.125</v>
+      </c>
+      <c r="AC190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL190" s="6">
+        <v>1</v>
+      </c>
+      <c r="AM190" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN190" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO190" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP190" s="4">
         <v>58</v>
       </c>
@@ -28562,7 +30232,7 @@
         <v>19944</v>
       </c>
       <c r="B195" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C195" s="4">
         <v>51</v>
@@ -28592,14 +30262,26 @@
         <v>58</v>
       </c>
       <c r="L195" s="4"/>
-      <c r="M195" s="5"/>
-      <c r="N195" s="6"/>
+      <c r="M195" s="5">
+        <v>3466.1500000000001</v>
+      </c>
+      <c r="N195" s="6">
+        <v>45</v>
+      </c>
       <c r="O195" s="6"/>
-      <c r="P195" s="7"/>
-      <c r="Q195" s="8"/>
-      <c r="R195" s="8"/>
+      <c r="P195" s="7">
+        <v>4.1811974358974355</v>
+      </c>
+      <c r="Q195" s="8">
+        <v>17.139742307692309</v>
+      </c>
+      <c r="R195" s="8">
+        <v>6.0012807692307693</v>
+      </c>
       <c r="S195" s="8"/>
-      <c r="T195" s="9"/>
+      <c r="T195" s="9">
+        <v>0.38461538461538464</v>
+      </c>
       <c r="U195" s="9"/>
       <c r="V195" s="9"/>
       <c r="W195" s="9"/>
@@ -29132,7 +30814,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>51</v>
@@ -29162,35 +30844,93 @@
         <v>58</v>
       </c>
       <c r="L199" s="4"/>
-      <c r="M199" s="5"/>
-      <c r="N199" s="6"/>
-      <c r="O199" s="6"/>
-      <c r="P199" s="7"/>
-      <c r="Q199" s="8"/>
-      <c r="R199" s="8"/>
-      <c r="S199" s="8"/>
-      <c r="T199" s="9"/>
-      <c r="U199" s="9"/>
-      <c r="V199" s="9"/>
-      <c r="W199" s="9"/>
-      <c r="X199" s="9"/>
-      <c r="Y199" s="9"/>
-      <c r="Z199" s="9"/>
-      <c r="AA199" s="9"/>
-      <c r="AB199" s="9"/>
-      <c r="AC199" s="9"/>
-      <c r="AD199" s="6"/>
-      <c r="AE199" s="6"/>
-      <c r="AF199" s="6"/>
-      <c r="AG199" s="6"/>
-      <c r="AH199" s="6"/>
-      <c r="AI199" s="6"/>
-      <c r="AJ199" s="6"/>
-      <c r="AK199" s="6"/>
-      <c r="AL199" s="6"/>
-      <c r="AM199" s="6"/>
-      <c r="AN199" s="9"/>
-      <c r="AO199" s="6"/>
+      <c r="M199" s="5">
+        <v>2721.79</v>
+      </c>
+      <c r="N199" s="6">
+        <v>35</v>
+      </c>
+      <c r="O199" s="6">
+        <v>15</v>
+      </c>
+      <c r="P199" s="7">
+        <v>3.8300000000000005</v>
+      </c>
+      <c r="Q199" s="8">
+        <v>12.315553333333334</v>
+      </c>
+      <c r="R199" s="8">
+        <v>1.3933333333333333</v>
+      </c>
+      <c r="S199" s="8">
+        <v>7</v>
+      </c>
+      <c r="T199" s="9">
+        <v>0.80000000000000004</v>
+      </c>
+      <c r="U199" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="V199" s="9">
+        <v>0</v>
+      </c>
+      <c r="W199" s="9">
+        <v>0</v>
+      </c>
+      <c r="X199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y199" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB199" s="9">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="AC199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL199" s="6">
+        <v>2</v>
+      </c>
+      <c r="AM199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN199" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO199" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP199" s="4">
         <v>58</v>
       </c>
@@ -30057,7 +31797,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>51</v>
@@ -30087,35 +31827,93 @@
         <v>58</v>
       </c>
       <c r="L206" s="4"/>
-      <c r="M206" s="5"/>
-      <c r="N206" s="6"/>
-      <c r="O206" s="6"/>
-      <c r="P206" s="7"/>
-      <c r="Q206" s="8"/>
-      <c r="R206" s="8"/>
-      <c r="S206" s="8"/>
-      <c r="T206" s="9"/>
-      <c r="U206" s="9"/>
-      <c r="V206" s="9"/>
-      <c r="W206" s="9"/>
-      <c r="X206" s="9"/>
-      <c r="Y206" s="9"/>
-      <c r="Z206" s="9"/>
-      <c r="AA206" s="9"/>
-      <c r="AB206" s="9"/>
-      <c r="AC206" s="9"/>
-      <c r="AD206" s="6"/>
-      <c r="AE206" s="6"/>
-      <c r="AF206" s="6"/>
-      <c r="AG206" s="6"/>
-      <c r="AH206" s="6"/>
-      <c r="AI206" s="6"/>
-      <c r="AJ206" s="6"/>
-      <c r="AK206" s="6"/>
-      <c r="AL206" s="6"/>
-      <c r="AM206" s="6"/>
-      <c r="AN206" s="9"/>
-      <c r="AO206" s="6"/>
+      <c r="M206" s="5">
+        <v>1361.46</v>
+      </c>
+      <c r="N206" s="6">
+        <v>18</v>
+      </c>
+      <c r="O206" s="6">
+        <v>6</v>
+      </c>
+      <c r="P206" s="7">
+        <v>6.3470588235294123</v>
+      </c>
+      <c r="Q206" s="8">
+        <v>16.849999999999998</v>
+      </c>
+      <c r="R206" s="8">
+        <v>2.1916666666666669</v>
+      </c>
+      <c r="S206" s="8">
+        <v>7</v>
+      </c>
+      <c r="T206" s="9">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="U206" s="9">
+        <v>0</v>
+      </c>
+      <c r="V206" s="9">
+        <v>0</v>
+      </c>
+      <c r="W206" s="9">
+        <v>0</v>
+      </c>
+      <c r="X206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y206" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AF206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM206" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN206" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO206" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP206" s="4">
         <v>58</v>
       </c>

--- a/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-22).xlsx
+++ b/novo projeto/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-22).xlsx
@@ -935,16 +935,16 @@
     <t>214</t>
   </si>
   <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 4.988,97</t>
-  </si>
-  <si>
-    <t>52.6</t>
-  </si>
-  <si>
-    <t>30.9</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 5.043,17</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>31.3</t>
   </si>
   <si>
     <t>5.35</t>
@@ -956,13 +956,13 @@
     <t>6.3</t>
   </si>
   <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>42.4%</t>
-  </si>
-  <si>
-    <t>16.0%</t>
+    <t>6.2</t>
+  </si>
+  <si>
+    <t>41.7%</t>
+  </si>
+  <si>
+    <t>16.1%</t>
   </si>
   <si>
     <t>1.6%</t>
@@ -971,7 +971,7 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>3.6%</t>
+    <t>3.5%</t>
   </si>
   <si>
     <t>1.3%</t>
@@ -980,28 +980,28 @@
     <t>0.2%</t>
   </si>
   <si>
-    <t>6.4%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>3.0%</t>
-  </si>
-  <si>
-    <t>1083.0</t>
-  </si>
-  <si>
-    <t>875.0</t>
-  </si>
-  <si>
-    <t>89.0</t>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>3.1%</t>
+  </si>
+  <si>
+    <t>1130.0</t>
+  </si>
+  <si>
+    <t>921.0</t>
+  </si>
+  <si>
+    <t>93.0</t>
   </si>
   <si>
     <t>26.0</t>
   </si>
   <si>
-    <t>199.0</t>
+    <t>202.0</t>
   </si>
   <si>
     <t>73.0</t>
@@ -1010,13 +1010,13 @@
     <t>13.0</t>
   </si>
   <si>
-    <t>351.0</t>
-  </si>
-  <si>
-    <t>157.0</t>
-  </si>
-  <si>
-    <t>163.0</t>
+    <t>370.0</t>
+  </si>
+  <si>
+    <t>162.0</t>
+  </si>
+  <si>
+    <t>179.0</t>
   </si>
   <si>
     <t>0.7%</t>
@@ -3242,7 +3242,7 @@
         <v>19515</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -3272,35 +3272,93 @@
         <v>58</v>
       </c>
       <c r="L13" s="4"/>
-      <c r="M13" s="5"/>
-      <c r="N13" s="6"/>
-      <c r="O13" s="6"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="8"/>
-      <c r="T13" s="9"/>
-      <c r="U13" s="9"/>
-      <c r="V13" s="9"/>
-      <c r="W13" s="9"/>
-      <c r="X13" s="9"/>
-      <c r="Y13" s="9"/>
-      <c r="Z13" s="9"/>
-      <c r="AA13" s="9"/>
-      <c r="AB13" s="9"/>
-      <c r="AC13" s="9"/>
-      <c r="AD13" s="6"/>
-      <c r="AE13" s="6"/>
-      <c r="AF13" s="6"/>
-      <c r="AG13" s="6"/>
-      <c r="AH13" s="6"/>
-      <c r="AI13" s="6"/>
-      <c r="AJ13" s="6"/>
-      <c r="AK13" s="6"/>
-      <c r="AL13" s="6"/>
-      <c r="AM13" s="6"/>
-      <c r="AN13" s="9"/>
-      <c r="AO13" s="6"/>
+      <c r="M13" s="5">
+        <v>10730.66</v>
+      </c>
+      <c r="N13" s="6">
+        <v>104</v>
+      </c>
+      <c r="O13" s="6">
+        <v>78</v>
+      </c>
+      <c r="P13" s="7">
+        <v>6.5258009615384616</v>
+      </c>
+      <c r="Q13" s="8">
+        <v>21.740170512820516</v>
+      </c>
+      <c r="R13" s="8">
+        <v>7.9318371794871796</v>
+      </c>
+      <c r="S13" s="8">
+        <v>7</v>
+      </c>
+      <c r="T13" s="9">
+        <v>0.20512820512820512</v>
+      </c>
+      <c r="U13" s="9">
+        <v>0.25641025641025639</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="9">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="Y13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>0.064102564102564097</v>
+      </c>
+      <c r="AC13" s="9">
+        <v>0.17948717948717949</v>
+      </c>
+      <c r="AD13" s="6">
+        <v>20</v>
+      </c>
+      <c r="AE13" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM13" s="6">
+        <v>14</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP13" s="4">
         <v>58</v>
       </c>
@@ -7609,7 +7667,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>51</v>
@@ -7639,35 +7697,93 @@
         <v>58</v>
       </c>
       <c r="L42" s="4"/>
-      <c r="M42" s="5"/>
-      <c r="N42" s="6"/>
-      <c r="O42" s="6"/>
-      <c r="P42" s="7"/>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="8"/>
-      <c r="T42" s="9"/>
-      <c r="U42" s="9"/>
-      <c r="V42" s="9"/>
-      <c r="W42" s="9"/>
-      <c r="X42" s="9"/>
-      <c r="Y42" s="9"/>
-      <c r="Z42" s="9"/>
-      <c r="AA42" s="9"/>
-      <c r="AB42" s="9"/>
-      <c r="AC42" s="9"/>
-      <c r="AD42" s="6"/>
-      <c r="AE42" s="6"/>
-      <c r="AF42" s="6"/>
-      <c r="AG42" s="6"/>
-      <c r="AH42" s="6"/>
-      <c r="AI42" s="6"/>
-      <c r="AJ42" s="6"/>
-      <c r="AK42" s="6"/>
-      <c r="AL42" s="6"/>
-      <c r="AM42" s="6"/>
-      <c r="AN42" s="9"/>
-      <c r="AO42" s="6"/>
+      <c r="M42" s="5">
+        <v>3256.8699999999999</v>
+      </c>
+      <c r="N42" s="6">
+        <v>35</v>
+      </c>
+      <c r="O42" s="6">
+        <v>27</v>
+      </c>
+      <c r="P42" s="7">
+        <v>6.8720588235294118</v>
+      </c>
+      <c r="Q42" s="8">
+        <v>18.867285185185185</v>
+      </c>
+      <c r="R42" s="8">
+        <v>4.0969148148148147</v>
+      </c>
+      <c r="S42" s="8">
+        <v>7</v>
+      </c>
+      <c r="T42" s="9">
+        <v>0.18518518518518517</v>
+      </c>
+      <c r="U42" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="V42" s="9">
+        <v>0</v>
+      </c>
+      <c r="W42" s="9">
+        <v>0</v>
+      </c>
+      <c r="X42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA42" s="9">
+        <v>0.037037037037037035</v>
+      </c>
+      <c r="AB42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK42" s="6">
+        <v>1</v>
+      </c>
+      <c r="AL42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM42" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN42" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP42" s="4">
         <v>58</v>
       </c>
@@ -9057,7 +9173,7 @@
         <v>19606</v>
       </c>
       <c r="B52" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C52" s="4">
         <v>51</v>
@@ -9087,35 +9203,93 @@
         <v>58</v>
       </c>
       <c r="L52" s="4"/>
-      <c r="M52" s="5"/>
-      <c r="N52" s="6"/>
-      <c r="O52" s="6"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="8"/>
-      <c r="R52" s="8"/>
-      <c r="S52" s="8"/>
-      <c r="T52" s="9"/>
-      <c r="U52" s="9"/>
-      <c r="V52" s="9"/>
-      <c r="W52" s="9"/>
-      <c r="X52" s="9"/>
-      <c r="Y52" s="9"/>
-      <c r="Z52" s="9"/>
-      <c r="AA52" s="9"/>
-      <c r="AB52" s="9"/>
-      <c r="AC52" s="9"/>
-      <c r="AD52" s="6"/>
-      <c r="AE52" s="6"/>
-      <c r="AF52" s="6"/>
-      <c r="AG52" s="6"/>
-      <c r="AH52" s="6"/>
-      <c r="AI52" s="6"/>
-      <c r="AJ52" s="6"/>
-      <c r="AK52" s="6"/>
-      <c r="AL52" s="6"/>
-      <c r="AM52" s="6"/>
-      <c r="AN52" s="9"/>
-      <c r="AO52" s="6"/>
+      <c r="M52" s="5">
+        <v>8431.1700000000001</v>
+      </c>
+      <c r="N52" s="6">
+        <v>71</v>
+      </c>
+      <c r="O52" s="6">
+        <v>34</v>
+      </c>
+      <c r="P52" s="7">
+        <v>4.2945945945945949</v>
+      </c>
+      <c r="Q52" s="8">
+        <v>13.491176470588234</v>
+      </c>
+      <c r="R52" s="8">
+        <v>1.4208343750000001</v>
+      </c>
+      <c r="S52" s="8">
+        <v>8</v>
+      </c>
+      <c r="T52" s="9">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="U52" s="9">
+        <v>0.14705882352941177</v>
+      </c>
+      <c r="V52" s="9">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="W52" s="9">
+        <v>0</v>
+      </c>
+      <c r="X52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="9">
+        <v>0.088235294117647065</v>
+      </c>
+      <c r="AB52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="6">
+        <v>6</v>
+      </c>
+      <c r="AE52" s="6">
+        <v>5</v>
+      </c>
+      <c r="AF52" s="6">
+        <v>3</v>
+      </c>
+      <c r="AG52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK52" s="6">
+        <v>3</v>
+      </c>
+      <c r="AL52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM52" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN52" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP52" s="4">
         <v>58</v>
       </c>
@@ -9973,7 +10147,9 @@
       <c r="N58" s="6">
         <v>75</v>
       </c>
-      <c r="O58" s="6"/>
+      <c r="O58" s="6">
+        <v>52</v>
+      </c>
       <c r="P58" s="7">
         <v>2.8065732394366196</v>
       </c>
@@ -9983,31 +10159,75 @@
       <c r="R58" s="8">
         <v>4.1423076923076927</v>
       </c>
-      <c r="S58" s="8"/>
+      <c r="S58" s="8">
+        <v>7</v>
+      </c>
       <c r="T58" s="9">
         <v>0.71153846153846156</v>
       </c>
-      <c r="U58" s="9"/>
-      <c r="V58" s="9"/>
-      <c r="W58" s="9"/>
-      <c r="X58" s="9"/>
-      <c r="Y58" s="9"/>
-      <c r="Z58" s="9"/>
-      <c r="AA58" s="9"/>
-      <c r="AB58" s="9"/>
-      <c r="AC58" s="9"/>
-      <c r="AD58" s="6"/>
-      <c r="AE58" s="6"/>
-      <c r="AF58" s="6"/>
-      <c r="AG58" s="6"/>
-      <c r="AH58" s="6"/>
-      <c r="AI58" s="6"/>
-      <c r="AJ58" s="6"/>
-      <c r="AK58" s="6"/>
-      <c r="AL58" s="6"/>
-      <c r="AM58" s="6"/>
-      <c r="AN58" s="9"/>
-      <c r="AO58" s="6"/>
+      <c r="U58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="V58" s="9">
+        <v>0.019230769230769232</v>
+      </c>
+      <c r="W58" s="9">
+        <v>0</v>
+      </c>
+      <c r="X58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN58" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO58" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP58" s="4">
         <v>58</v>
       </c>
@@ -12583,7 +12803,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>51</v>
@@ -12611,35 +12831,93 @@
         <v>58</v>
       </c>
       <c r="L76" s="4"/>
-      <c r="M76" s="5"/>
-      <c r="N76" s="6"/>
-      <c r="O76" s="6"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="8"/>
-      <c r="R76" s="8"/>
-      <c r="S76" s="8"/>
-      <c r="T76" s="9"/>
-      <c r="U76" s="9"/>
-      <c r="V76" s="9"/>
-      <c r="W76" s="9"/>
-      <c r="X76" s="9"/>
-      <c r="Y76" s="9"/>
-      <c r="Z76" s="9"/>
-      <c r="AA76" s="9"/>
-      <c r="AB76" s="9"/>
-      <c r="AC76" s="9"/>
-      <c r="AD76" s="6"/>
-      <c r="AE76" s="6"/>
-      <c r="AF76" s="6"/>
-      <c r="AG76" s="6"/>
-      <c r="AH76" s="6"/>
-      <c r="AI76" s="6"/>
-      <c r="AJ76" s="6"/>
-      <c r="AK76" s="6"/>
-      <c r="AL76" s="6"/>
-      <c r="AM76" s="6"/>
-      <c r="AN76" s="9"/>
-      <c r="AO76" s="6"/>
+      <c r="M76" s="5">
+        <v>7563.3400000000001</v>
+      </c>
+      <c r="N76" s="6">
+        <v>82</v>
+      </c>
+      <c r="O76" s="6">
+        <v>44</v>
+      </c>
+      <c r="P76" s="7">
+        <v>3.1172413793103448</v>
+      </c>
+      <c r="Q76" s="8">
+        <v>15.382954545454545</v>
+      </c>
+      <c r="R76" s="8">
+        <v>4.548147222222223</v>
+      </c>
+      <c r="S76" s="8">
+        <v>9</v>
+      </c>
+      <c r="T76" s="9">
+        <v>0.47727272727272729</v>
+      </c>
+      <c r="U76" s="9">
+        <v>0.40909090909090912</v>
+      </c>
+      <c r="V76" s="9">
+        <v>0</v>
+      </c>
+      <c r="W76" s="9">
+        <v>0</v>
+      </c>
+      <c r="X76" s="9">
+        <v>0.022727272727272728</v>
+      </c>
+      <c r="Y76" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="9">
+        <v>0.34090909090909088</v>
+      </c>
+      <c r="AB76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="9">
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="AD76" s="6">
+        <v>18</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH76" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK76" s="6">
+        <v>15</v>
+      </c>
+      <c r="AL76" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM76" s="6">
+        <v>2</v>
+      </c>
+      <c r="AN76" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO76" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP76" s="4">
         <v>58</v>
       </c>
@@ -27864,7 +28142,9 @@
       <c r="N179" s="6">
         <v>61</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>20</v>
+      </c>
       <c r="P179" s="7">
         <v>3.6939655172413794</v>
       </c>
@@ -27874,31 +28154,75 @@
       <c r="R179" s="8">
         <v>2.0033349999999999</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.80000000000000004</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0.050000000000000003</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
